--- a/output/Surveyors/Madhya Pradesh/Consolidated/Consolidated_Rejected_Notes.xlsx
+++ b/output/Surveyors/Madhya Pradesh/Consolidated/Consolidated_Rejected_Notes.xlsx
@@ -6,6 +6,10 @@
     <sheet name="9B - Credit   Debit Notes (Regi" sheetId="1" r:id="rId1"/>
     <sheet name="4A, 4B, 6B, 6C - B2B, SEZ, DE I" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'9B - Credit   Debit Notes (Regi'!A5:P7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'4A, 4B, 6B, 6C - B2B, SEZ, DE I'!A5:O8</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -35,7 +39,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="60" formatCode="dd-mm-yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -519,6 +523,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:P7"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:P7"/>
   </ignoredErrors>
@@ -686,6 +691,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:O8"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:O8"/>
   </ignoredErrors>
